--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trials\LearnSangeet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24763476-18C0-476A-81B8-22510C2B8CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523D9CE1-9720-46F1-9C20-EF7223818C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2955" windowWidth="29040" windowHeight="15720" xr2:uid="{6AF9BE09-3E11-4CB4-95D7-6623BDAC1D1F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6AF9BE09-3E11-4CB4-95D7-6623BDAC1D1F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,366 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>१</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>स</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <color rgb="FF1F2121"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>षड्जम्</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>२</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <color rgb="FF1F2121"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>ऋषभम्</t>
+    </r>
+  </si>
+  <si>
+    <t>शुद्ध</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>ऋ१</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>३</t>
+    </r>
+  </si>
+  <si>
+    <t>चतुश्रुति</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>ऋ२</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>ग१</t>
+    </r>
+  </si>
+  <si>
+    <t>गान्धारम्</t>
+  </si>
+  <si>
+    <t>Vivadi Swaras</t>
+  </si>
+  <si>
+    <t>https://youtu.be/kEToD1XASRk?t=355</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>४</t>
+    </r>
+  </si>
+  <si>
+    <t>षट्श्रुति</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>ऋ३</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>ग२</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <color rgb="FF1F2121"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>साधारण</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>५</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>ग३</t>
+    </r>
+  </si>
+  <si>
+    <t>अन्तर</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>६</t>
+    </r>
+  </si>
+  <si>
+    <t>मध्यमम्</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <color rgb="FF1F2121"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>म१</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>७</t>
+    </r>
+  </si>
+  <si>
+    <t>प्रति</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <color rgb="FF1F2121"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>म२</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>८</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <color rgb="FF1F2121"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>प</t>
+    </r>
+  </si>
+  <si>
+    <t>पञ्चमम्</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>९</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <color rgb="FF1F2121"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>धैवतम्</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>ध१</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>१०</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>ध२</t>
+    </r>
+  </si>
+  <si>
+    <t>नि१</t>
+  </si>
+  <si>
+    <t>निषादम्</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>११</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>ध३</t>
+    </r>
+  </si>
+  <si>
+    <t>नि२</t>
+  </si>
+  <si>
+    <t>कैशिकी</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>१२</t>
+    </r>
+  </si>
+  <si>
+    <t>नि३</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="28"/>
+        <color rgb="FF1F2121"/>
+        <rFont val="Nirmala UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>काकली</t>
+    </r>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -49,16 +403,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="28"/>
+      <name val="Nirmala UI"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <name val="Nirmala UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color rgb="FF1F2121"/>
+      <name val="Nirmala UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F9F9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -66,12 +451,115 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -406,12 +894,297 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47ED089C-B370-4F68-B616-2A612B1EF3DB}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:Q15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="9.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="24.44140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.5546875" style="2" customWidth="1"/>
+    <col min="5" max="6" width="12.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14" style="2" customWidth="1"/>
+    <col min="8" max="8" width="29.109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="28" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="2:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="2:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="2:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="L5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="12"/>
+      <c r="Q5" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="14"/>
+      <c r="J6" s="1"/>
+      <c r="L6" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="15"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="2:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="2:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="2:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="2:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="2:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="L12" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="1"/>
+      <c r="L13" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="I12:I14"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;11&amp;K008000 Baker Hughes Confidential</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>